--- a/data/CdS2/CdS2_IV Graph.xlsx
+++ b/data/CdS2/CdS2_IV Graph.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1" documentId="8_{7A774E2C-ACBB-43DE-93AF-1F18F81F6DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF4125E5-004D-4715-9DA9-D66CFC906E8F}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{7DAC3027-A08C-434A-BE69-654896B2AE62}"/>
+    <workbookView minimized="1" xWindow="2580" yWindow="2580" windowWidth="17280" windowHeight="8880" xr2:uid="{7DAC3027-A08C-434A-BE69-654896B2AE62}"/>
   </bookViews>
   <sheets>
     <sheet name="CdS2_IV Graph_1" sheetId="1" r:id="rId1"/>
@@ -644,6 +644,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
